--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reglas Normativas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tabla Ampacidad 310-15b16" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Normativas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla Ampacidad 310-15b16" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,384 @@
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>R-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>240-4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Proteccion de conductores segun ampacidad</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Se esta seleccionando el dispositivo de proteccion contra sobrecorriente (fusible o interruptor) de cualquier conductor que no sea cordon flexible, cable flexible ni alambre de luminaria.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>El valor nominal del dispositivo de proteccion no debe exceder la ampacidad del conductor determinada segun el Articulo 310-15 (ya corregida por temperatura y agrupamiento), salvo las excepciones de 240-4(a) a (g) (redondeo al valor estandar superior para protecciones &lt;=800A, topes para conductores pequenos, etc.).</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Calculo de ampacidad corregida del conductor + valor nominal del dispositivo elegido, mostrando que uno no excede al otro (o citando la excepcion aplicable de 240-4).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>R-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>240-6(a)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades estandar de fusibles e interruptores</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Se necesita expresar la proteccion contra sobrecorriente como un valor comercial (no un valor calculado arbitrario).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>El valor nominal debe tomarse de la lista de capacidades estandar de la Tabla 240-6(a): 15, 20, 25, 30, 35, 40, 45, 50, 60, 70, 80, 90, 100, 110, 125, 150, 175, 200, 225, 250, 300, 350, 400, 450, 500, 600, 700, 800, 1000, 1200, 1600, 2000, 2500, 3000 A (mas 1, 3, 6, 10 y 601 A solo para fusibles).</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Valor nominal del dispositivo especificado en el proyecto, verificado contra la lista de la Tabla 240-6(a).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-6(a), Tabla 240-6(a)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>R-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>240-8</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Fusibles o interruptores en paralelo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>El diseno propone dos o mas fusibles o interruptores automaticos individuales conectados en paralelo para aumentar la capacidad de proteccion.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>NO se permite conectar en paralelo fusibles individuales, interruptores automaticos o combinaciones de ellos, salvo que esten ensamblados en paralelo de fabrica y aprobados como una sola unidad.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ficha tecnica/listado del fabricante que confirme que el dispositivo es un ensamble aprobado como unidad, si se usa esta configuracion.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-8</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>R-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>240-9</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Dispositivos termicos no sustituyen proteccion contra sobrecorriente</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Se esta considerando un relevador termico u otro dispositivo que no esta disenado para abrir cortocircuitos o fallas a tierra como proteccion contra sobrecorriente del conductor.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Los dispositivos termicos NO deben usarse para proteccion contra sobrecorriente por cortocircuito o falla a tierra. Excepcion: se permite su uso para proteger contra SOBRECARGA los conductores del circuito derivado de un motor, si cumplen 430-40.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Especificacion del dispositivo de proteccion contra cortocircuito/falla a tierra independiente del relevador termico (salvo caso de motor bajo 430-40).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>R-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>240-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Proteccion de falla a tierra en acometidas/alimentadores grandes</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>El sistema es en estrella, solidamente puesto a tierra, con mas de 150 V a tierra pero no mas de 1000 V entre fases, y el medio principal de desconexion (acometida o edificio) tiene capacidad nominal de 1000 A o mayor.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Debe proporcionarse proteccion contra fallas a tierra del equipo, de acuerdo con 230-95, para cada dispositivo usado como medio principal de desconexion. No aplica a procesos industriales continuos donde un paro no ordenado incremente riesgos, instalaciones ya protegidas por otros requisitos, ni bombas contra incendio.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Memoria que muestre tension del sistema, capacidad del medio de desconexion, y especificacion del dispositivo de proteccion de falla a tierra instalado (o justificacion de excepcion aplicable).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-13</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>R-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>240-21</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Ubicacion de la proteccion contra sobrecorriente</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Se esta definiendo en que punto del circuito se instala el dispositivo de proteccion contra sobrecorriente.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>La proteccion debe ubicarse en el punto donde el conductor recibe su alimentacion (origen del circuito), salvo las excepciones de derivaciones/taps de 240-21(a) a (h) (p. ej. derivaciones no mayores a 3.00 m que cumplan ampacidad minima y esten en canalizacion, entre otras condiciones especificas por tipo de derivacion).</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Diagrama unifilar o plano que muestre la ubicacion del dispositivo de proteccion respecto al origen del conductor; si se usa una excepcion de derivacion, memoria que confirme el cumplimiento de las condiciones especificas de esa excepcion (longitud, ampacidad minima, canalizacion, etc.).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-21</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>R-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>240-24(a)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad y altura de dispositivos de sobrecorriente</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Se esta definiendo la ubicacion fisica de un interruptor o interruptor automatico en la instalacion.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>El dispositivo debe quedar facilmente accesible, y el centro de la manija de operacion, en su posicion mas alta, no debe quedar a mas de 2.00 m sobre el piso o plataforma de trabajo (salvo las excepciones de 240-24(a)(1) a (4): electroductos, proteccion suplementaria, dispositivos de acometida segun 225-40/230-92, o acceso por medios portatiles junto al equipo que alimentan).</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Plano o verificacion en sitio de la altura de montaje del centro de la manija del dispositivo (medicion en metros desde el piso terminado).</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-24(a)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>R-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>240-24(c-f)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Ubicaciones prohibidas para dispositivos de sobrecorriente</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Se esta eligiendo el sitio donde se instalara un interruptor, interruptor automatico o centro de carga.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>El dispositivo NO debe quedar: (c) expuesto a dano fisico; (d) cerca de material facilmente inflamable (p. ej. closets de ropa); (e) dentro de cuartos de bano, en unidades de vivienda, dormitorios o habitaciones/suites de huesped; (f) sobre los peldanos de una escalera.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fotografia o plano de la ubicacion final del tablero/interruptor mostrando que no incurre en ninguna de las 4 condiciones prohibidas.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-24, incisos c), d), e) y f)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>R-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>240-33</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Posicion de las envolventes de proteccion</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Se esta instalando la envolvente (gabinete) de un dispositivo de proteccion contra sobrecorriente.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>La envolvente debe instalarse en posicion VERTICAL, a menos que se demuestre que es impractico. Excepcion: se permite horizontal si el interruptor automatico esta instalado conforme a 240-81 (interruptores especificamente disenados/aprobados para montaje horizontal).</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Fotografia o verificacion en sitio de la orientacion de montaje del gabinete/centro de carga.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 240-33</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Normativas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla Ampacidad 310-15b16" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tablas Art 220" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,11 @@
       <name val="Arial"/>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -96,6 +102,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1225,6 +1232,468 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>R-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>220-12</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Carga minima de alumbrado general por m2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Se esta calculando la carga de alumbrado general de un inmueble (cualquier tipo: vivienda, oficina, escuela, tienda, etc.).</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>La carga minima debe ser &gt;= la carga unitaria en VA/m2 de la Tabla 220-12 segun el tipo de inmueble (ver hoja 'Tablas Art 220'), multiplicada por el area del piso calculada con dimensiones EXTERIORES del edificio. En vivienda no se cuentan patios abiertos, cocheras ni espacios sin terminar no adaptables.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Plano con el area de piso por nivel (m2, dimensiones exteriores), tipo de inmueble declarado, y la carga de alumbrado general resultante en VA.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-12, Tabla 220-12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>R-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>220-14(i)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Carga por salida de contacto</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Se esta calculando la carga de salidas de contactos de uso general (fuera de vivienda, o en vivienda cuando no aplica 220-14(j)).</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Cada contacto sencillo o multiple montado en el mismo yugo se calcula con minimo 180 VA. Un contacto multiple de cuatro o mas contactos se calcula con minimo 90 VA por cada contacto.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Conteo de salidas de contacto por circuito/tablero y la carga en VA asignada a cada una.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-14(i)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>R-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>220-14(j)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Contactos en vivienda ya incluidos en alumbrado general</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>El inmueble es vivienda unifamiliar, bifamiliar, multifamiliar, o habitacion/suite de huespedes de hotel o motel.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>NO se debe sumar carga adicional por las salidas de contactos de uso general de 20 A o menos ni por las salidas de alumbrado de 210-70: ya estan incluidas en la carga de alumbrado general calculada con 220-12 (Tabla 220-12, 33 VA/m2 para vivienda). Sumarlas aparte es un error de doble conteo.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Memoria de calculo que muestre que la carga de contactos de uso general no se sumo por separado a los VA/m2 de alumbrado general.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-14(j)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>R-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>220-18(a)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Carga total con motores: 125% del motor mayor</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Un circuito alimenta equipo accionado por motor fijo en sitio de mas de 93.25 W (1/8 HP) en combinacion con otras cargas.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>La carga total calculada debe basarse en 125% de la carga del motor MAS GRANDE, mas la suma de las otras cargas (los demas motores y cargas se suman al 100%). Si el circuito alimenta SOLO motores aplica el Art. 430; si alimenta solo aire acondicionado/refrigeracion aplica el Art. 440.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Memoria que identifique el motor mas grande del circuito, el 125% aplicado a el, y la suma del resto de cargas al 100%.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-18(a)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>R-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>220-42</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Factores de demanda de alumbrado general</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Se esta calculando la carga de un ALIMENTADOR o ACOMETIDA (no de un circuito derivado) y ya se tiene la carga de alumbrado general.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar los factores de demanda de la Tabla 220-42 por escalones segun tipo de inmueble (ver hoja 'Tablas Art 220'). Ej. vivienda: 100% de los primeros 3000 VA, 35% de 3001 a 120000 VA, 25% del excedente. ATENCION: estos factores NO se deben aplicar para determinar el NUMERO de circuitos derivados de alumbrado.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Memoria con la carga de alumbrado general antes y despues de aplicar la demanda, mostrando el desglose por escalones y el tipo de inmueble usado.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-42, Tabla 220-42</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>R-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>220-44</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Factores de demanda de contactos (no vivienda)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Se calcula el alimentador/acometida de un inmueble que NO es vivienda y se tiene la carga de contactos calculada con 220-14(h) e (i).</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Se permite aplicar los factores de demanda de la Tabla 220-44: 100% de los primeros 10 kVA y 50% del excedente. Alternativamente se pueden aplicar los factores de la Tabla 220-42.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Memoria con la carga total de contactos y el desglose del factor de demanda aplicado (primeros 10 kVA al 100%, resto al 50%).</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-44, Tabla 220-44</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>R-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>220-51</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Calefaccion electrica fija de ambiente</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>El inmueble tiene calefaccion electrica fija de ambiente.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>La carga se calcula al 100% de la carga total conectada (sin factor de demanda). Ademas, la corriente nominal de la acometida/alimentador nunca debe ser menor al valor nominal del circuito derivado mas grande que alimenta. Excepcion: se permite menos del 100% si los equipos operan por ciclos o no todos a la vez, siempre que los conductores tengan ampacidad para la carga asi calculada.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Listado de equipos de calefaccion con su capacidad nominal, carga total al 100%, y comparacion contra el circuito derivado mayor.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-51</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>R-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>220-52</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Circuitos de aparatos pequenos y lavadora en vivienda</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Unidad de vivienda MAYOR a 60 m2 (la seccion no aplica a viviendas de 60 m2 o menos).</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Debe incluirse 1500 VA por cada circuito derivado de 2 hilos para aparatos pequenos (210-11(c)(1)) y 1500 VA por cada circuito derivado de 2 hilos para lavadora (210-11(c)(2)). Estas cargas pueden incluirse junto con la de alumbrado general y aplicarles los factores de demanda de la Tabla 220-42.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Memoria que liste los circuitos de aparatos pequenos y de lavadora considerados, con 1500 VA asignados a cada uno.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-52</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>R-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>220-53</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Factor de demanda para aparatos fijos en vivienda</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Vivienda unifamiliar, bifamiliar o multifamiliar con CUATRO O MAS aparatos fijos conectados al mismo alimentador.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Se permite aplicar un factor de demanda del 75% a la suma de las capacidades de placa de datos de esos aparatos. NO se incluyen en este 75%: estufas electricas, secadoras de ropa, equipo de calefaccion electrica ni aire acondicionado (esos tienen sus propias reglas).</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Listado de aparatos fijos con su capacidad de placa, conteo (&gt;=4) y el 75% aplicado, dejando fuera estufas, secadoras, calefaccion y A/A.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-53</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>R-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>220-60</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Cargas no coincidentes</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>El alimentador o acometida alimenta dos o mas cargas que no es probable que operen simultaneamente (p. ej. calefaccion y aire acondicionado).</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Se permite omitir del calculo la MENOR de las dos cargas no coincidentes.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Justificacion tecnica de por que las cargas no pueden ser simultaneas, e indicacion de cual se omitio del calculo.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-60</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>R-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>220-61</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Carga del neutro del alimentador o acometida</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Se esta dimensionando el conductor neutro de un alimentador o acometida.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>La carga del neutro es el MAXIMO DESEQUILIBRIO: la carga neta maxima calculada entre el neutro y cualquier conductor de fase. Reduccion permitida: factor adicional de 70% sobre la parte correspondiente a estufas/secadoras (Tablas 220-54 y 220-55) y sobre la parte del desequilibrio que exceda 200 A. PROHIBIDO reducir: en circuitos de 3 hilos formados por neutro + 2 fases de un sistema 3F-4H estrella, y en la parte que alimente cargas NO LINEALES en sistemas 3F-4H estrella (ahi el neutro puede requerir incluso mayor capacidad por armonicas).</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Memoria de calculo del desequilibrio maximo, con las reducciones aplicadas o la justificacion de por que no se redujo (cargas no lineales, sistema estrella 3F-4H).</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-61</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>
@@ -2123,4 +2592,587 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 220-12.- Cargas de alumbrado general por tipo de inmueble</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de inmueble</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Carga unitaria (VA/m2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bancos</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Casas de huespedes</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Clubes</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Cuarteles y auditorios</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Depositos (almacenamiento)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Edificios de oficinas</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Edificios industriales y comerciales (lugares de almacenamiento)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Escuelas</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Estacionamientos comerciales</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hospitales</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Hoteles y moteles, incluidos apartamentos sin cocineta</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Iglesias</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Juzgados</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Peluquerias y salones de belleza</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Restaurantes</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Tiendas</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Unidades de vivienda (ver 220-14(j))</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Vestibulos, pasillos, closets, escaleras (excepto vivienda)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Lugares de reunion y auditorios (excepto vivienda)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bodegas (excepto vivienda)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 220-42.- Factores de demanda de cargas de alumbrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de inmueble</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Parte de la carga (VA)</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>Factor de demanda (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Almacenes</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Primeros 12,500 o menos</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Almacenes</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>A partir de 12,500</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Hospitales*</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Primeros 50,000 o menos</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Hospitales*</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A partir de 50,000</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Hoteles y moteles (incl. apartamentos sin cocina)*</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Primeros 20,000 o menos</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Hoteles y moteles (incl. apartamentos sin cocina)*</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>De 20,001 a 100,000</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Hoteles y moteles (incl. apartamentos sin cocina)*</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>A partir de 100,000</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Unidades de vivienda</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Primeros 3,000 o menos</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Unidades de vivienda</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>De 3,001 a 120,000</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Unidades de vivienda</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>A partir de 120,000</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Todos los demas</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Voltamperes totales</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>* No aplicar estos factores a alimentadores de zonas donde puede usarse todo el alumbrado al mismo tiempo (quirofanos, comedores, salones de baile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 220-44.- Factores de demanda para contactos (inmuebles que NO son vivienda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Parte de la carga de contactos (VA)</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Factor de demanda (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Primeros 10 kVA o menos</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A partir de 10 kVA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 220-54.- Factores de demanda para secadoras domesticas de ropa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Numero de secadoras</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Factor de demanda (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Carga minima por secadora: 5000 VA o la placa de datos, la que sea mayor (Art. 220-54).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A39:C39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Normativas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla Ampacidad 310-15b16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tablas Art 220" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tablas Art 250" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1694,6 +1695,426 @@
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>R-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>250-52(a)(5)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Electrodos de varilla y tubería</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Se usara una varilla o tubo como electrodo de puesta a tierra.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>El electrodo debe tener minimo 2.44 m de longitud. Si es tubo/tubo conduit, no menor a designacion 21 (tamano comercial 3/4) y si es de acero debe estar galvanizado o con otro recubrimiento contra corrosion. Si es varilla de acero inoxidable o acero recubierto de cobre o zinc, minimo 16 mm de diametro. El electrodo debe estar libre de recubrimientos no conductores (pintura, esmalte).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Ficha tecnica/factura del electrodo (longitud, diametro, material y recubrimiento) y fotografia de la instalacion antes del relleno.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-52(a)(5) y 250-53(a)(1)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>R-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>250-53(a)(2)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Electrodo complementario obligatorio</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>El sistema de puesta a tierra se resolvera con UN SOLO electrodo de varilla, tubería o placa.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Un solo electrodo de varilla, tubería o placa DEBE complementarse con un electrodo adicional de los tipos de 250-52(a)(2) a (a)(8). EXCEPCION: no se requiere el electrodo adicional si se mide y demuestra que la resistencia a tierra del electrodo unico es de 25 ohms o menos.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Reporte de medicion de resistencia a tierra (telurometro) con valor &lt;= 25 ohms, o evidencia fotografica del segundo electrodo instalado y conectado.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-53(a)(2) y su Excepcion</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>R-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>250-53(a)(3)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Separación mínima entre electrodos</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Se instalaran dos o mas electrodos de varilla, tubería o placa.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Los electrodos deben estar separados cuando menos 1.80 m entre si. NOTA de la norma: la eficiencia aumenta separandolos 2 veces la longitud de la varilla mas larga (p. ej. ~4.9 m para varillas de 2.44 m). Ademas, cada electrodo debe estar a no menos de 1.80 m de electrodos de otros sistemas de puesta a tierra (incluidos pararrayos).</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Plano o croquis acotado de la ubicacion de los electrodos mostrando la separacion real en metros.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-53(a)(3) y 250-53(b)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>R-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>250-52(a)(3)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Electrodo recubierto en concreto (tipo Ufer)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Se aprovechara el acero de refuerzo de la cimentacion como electrodo de puesta a tierra.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Debe consistir en al menos 6.00 m de: varilla de refuerzo de acero desnuda o galvanizada de minimo 13 mm de diametro (continua o unida por amarre/soldadura), O conductor de cobre desnudo de minimo 21.2 mm2 (4 AWG). Los componentes deben tener minimo 5 cm de recubrimiento de concreto y estar horizontales en la cimentacion o zapata en contacto DIRECTO con la tierra (no cuenta si hay aislante, barrera de vapor o pelicula que separe el concreto del suelo).</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Fotografias de la armadura/conductor antes del colado, mostrando longitud, diametro y la conexion; nota en plano de cimentacion.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-52(a)(3)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>R-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>250-66</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Tamaño del conductor del electrodo de puesta a tierra</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Se dimensiona el conductor que va del sistema al electrodo de puesta a tierra (en acometida, edificio alimentado, o sistema derivado separado).</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>El tamano no debe ser menor al de la Tabla 250-66, segun el mayor conductor de entrada de acometida (ver hoja 'Tablas Art 250'). TOPES: si el conductor conecta UNICAMENTE a electrodos de varilla, tubería o placa, no se exige mayor a 13.3 mm2 (6 AWG) de cobre o 21.2 mm2 (4 AWG) de aluminio; si conecta unicamente a electrodo recubierto de concreto, no se exige mayor a 21.2 mm2 (4 AWG) de cobre.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Memoria con el calibre del mayor conductor de acometida, el calibre resultante de la Tabla 250-66 y el tope aplicado si corresponde.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-66, Tabla 250-66</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>R-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>250-122(a)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Tamaño del conductor de puesta a tierra de equipos</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Se dimensiona el conductor de puesta a tierra de equipos (tierra fisica del circuito) de cualquier circuito derivado o alimentador.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>El calibre no debe ser menor al de la Tabla 250-122, entrando con la CAPACIDAD DEL DISPOSITIVO DE PROTECCION del circuito (no con la corriente) — ver hoja 'Tablas Art 250'. Pero en ningun caso se exige que sea mayor que los conductores de fase del circuito.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Memoria que muestre el interruptor del circuito, el calibre de tierra obtenido de la Tabla 250-122 y la verificacion de que no excede el calibre de fase.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-122(a), Tabla 250-122</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>R-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>250-122(b)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Aumento proporcional del conductor de tierra</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Se aumento el calibre de los conductores de fase por encima del minimo requerido por ampacidad (caso tipico: se subio de calibre para cumplir el 3% de caida de tension en un circuito largo).</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>El conductor de puesta a tierra de equipos tipo alambre DEBE aumentarse proporcionalmente al area (mm2 o kcmil) en que se aumentaron los conductores de fase. Ejemplo: si la fase paso de 10 AWG (5.26 mm2) a 8 AWG (8.37 mm2), factor = 8.37/5.26 = 1.59, y el area de tierra minima de tabla debe multiplicarse por ese factor.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Memoria con: calibre de fase minimo por ampacidad, calibre de fase finalmente adoptado, factor de aumento calculado, y calibre de tierra resultante.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-122(b)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>R-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>250-122(c)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Tierra única para circuitos múltiples</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Un solo conductor de puesta a tierra de equipos se instalara para varios circuitos que comparten la misma canalizacion, cable o charola.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Ese conductor unico debe dimensionarse con base en el MAYOR dispositivo de proteccion contra sobrecorriente presente en esa canalizacion, cable o charola.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Listado de circuitos que comparten la canalizacion con sus interruptores, identificando el mayor, y el calibre de tierra resultante de la Tabla 250-122.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-122(c)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>R-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>250-124(b)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Prohibido interrumpir el conductor de tierra</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Se esta disenando el sistema de desconexion de un circuito o equipo.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>NO se debe colocar ningun cortacircuito automatico ni desconectador en el conductor de puesta a tierra de equipos, a menos que su apertura desconecte TODAS las fuentes de alimentacion. La tierra debe permanecer continua.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Diagrama unifilar que muestre el conductor de puesta a tierra sin dispositivos de interrupcion en su trayectoria.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-124(b)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>R-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>250-126</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de la terminal de tierra</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Se instalan dispositivos (contactos, apagadores, equipos) con terminal para conductor de puesta a tierra.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>La terminal de conexion del conductor de puesta a tierra de equipos debe identificarse por: (1) tornillo con cabeza de color VERDE no facilmente removible, (2) tuerca de color VERDE no facilmente removible, o (3) el simbolo de puesta a tierra indicado en la Figura 250-126.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Fotografia o ficha del dispositivo mostrando la identificacion verde o el simbolo de tierra en la terminal.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 250-126</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>
@@ -3175,4 +3596,534 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 250-66.- Conductor del electrodo de puesta a tierra (sistemas de corriente alterna)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Mayor conductor de acometida - Cobre</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mayor conductor de acometida - Aluminio</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Conductor al electrodo - Cobre</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Conductor al electrodo - Aluminio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2 AWG o menor (33.6 mm2)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1/0 AWG o menor (53.5 mm2)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>8 AWG (8.37 mm2)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>6 AWG (13.3 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1 o 1/0 AWG (42.4 o 53.5 mm2)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2/0 o 3/0 AWG (67.4 o 85.0 mm2)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6 AWG (13.3 mm2)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4 AWG (21.2 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2/0 o 3/0 AWG (67.4 o 85.0 mm2)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4/0 AWG o 250 kcmil (107 o 127 mm2)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4 AWG (21.2 mm2)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2 AWG (33.6 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 3/0 a 350 kcmil</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 250 a 500 kcmil</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2 AWG (33.6 mm2)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1/0 AWG (53.5 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 350 a 600 kcmil</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 500 a 900 kcmil</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1/0 AWG (53.5 mm2)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3/0 AWG (85.0 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 600 a 1100 kcmil</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 900 a 1750 kcmil</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2/0 AWG (67.4 mm2)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4/0 AWG (107 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 1100 kcmil</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Mas de 1750 kcmil</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3/0 AWG (85.0 mm2)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>250 kcmil (127 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Topes (250-66 a,b,c): si el conductor va UNICAMENTE a varilla/tubería/placa, no se exige mayor a 6 AWG Cu / 4 AWG Al. Si va unicamente a electrodo recubierto de concreto, no se exige mayor a 4 AWG Cu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 250-122.- Tamaño mínimo del conductor de puesta a tierra de equipos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Capacidad del dispositivo de protección (A), sin exceder</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Cobre</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Aluminio o Al recubierto de Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>14 AWG (2.08 mm2)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12 AWG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>12 AWG (3.31 mm2)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10 AWG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>10 AWG (5.26 mm2)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8 AWG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>8 AWG (8.37 mm2)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6 AWG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>6 AWG (13.3 mm2)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4 AWG (21.2 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>4 AWG (21.2 mm2)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2 AWG (33.6 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>3 AWG (26.7 mm2)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1 AWG (42.4 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2 AWG (33.6 mm2)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1/0 AWG (53.5 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1 AWG (42.4 mm2)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2/0 AWG (67.4 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1/0 AWG (53.5 mm2)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3/0 AWG (85.0 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2/0 AWG (67.4 mm2)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4/0 AWG (107 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>3/0 AWG (85.0 mm2)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>250 kcmil (127 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>4/0 AWG (107 mm2)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>350 kcmil (177 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>250 kcmil (127 mm2)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>400 kcmil (203 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>350 kcmil (177 mm2)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>600 kcmil (304 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>400 kcmil (203 mm2)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>600 kcmil (304 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>500 kcmil (253 mm2)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>750 kcmil (380 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>700 kcmil (355 mm2)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1200 kcmil (608 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>800 kcmil (405 mm2)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1200 kcmil (608 mm2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Se entra a esta tabla con la CAPACIDAD DEL INTERRUPTOR, no con la corriente. El conductor de tierra nunca debe exceder el calibre de fase (250-122a), y debe aumentarse proporcionalmente si se aumento el calibre de fase (250-122b).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla Ampacidad 310-15b16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tablas Art 220" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tablas Art 250" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas de validación" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +48,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E2761"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005A5F7A"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -89,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -104,6 +117,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4126,4 +4143,176 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Notas de validación — hallazgos al comparar ElectroNOM contra memorias de cálculo reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Estas notas NO son reglas normativas: son diferencias detectadas entre lo que calcula ElectroNOM (con base en la NOM-001-SEDE-2018) y lo que aparece en documentos de proyectos ya ejecutados. Sirven para decidir criterios de diseño y detectar errores de método.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Documento / circuito</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Hallazgo</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Análisis normativo</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Impacto</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="210" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>N-001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Memoria Jardín de Eventos CENTURA (27-nov-2025) — Alimentador Centro de carga D (fuerza, contactos y alumbrado oficina). Trifásico 220 V, 4,640 W, factor de carga 0.8, FP 0.9, 130 m, ambiente 40 °C.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>El documento especifica 4 AWG de cobre para fase y neutro, presentándolo como el calibre mínimo que cumple el 3% de caída de tensión. ElectroNOM calcula que 8 AWG ya cumple (2.65%).</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Se detectaron DOS desviaciones independientes:
+1) El documento usa la CORRIENTE CORREGIDA (Icorr = 15 A) en la fórmula de caída de tensión. Esto es un error de método: los factores de temperatura (0.91) y agrupamiento (0.8) sirven para degradar la AMPACIDAD del conductor (Art. 310-15(b)(2) y (b)(3)(a)), no para inflar la corriente que realmente circula. Por el conductor pasan 10.9 A reales. Usar 15 A cuenta dos veces el castigo por derateo.
+2) Aun aceptando su propio método (15 A y su fórmula que solo usa R), el resultado debería ser 6 AWG (2.47%), no 4 AWG — el 8 AWG falla con 3.93% pero el 6 AWG pasa. El salto hasta 4 AWG no está justificado en el documento.
+La única hipótesis que aterriza exactamente en 4 AWG es haber usado 260 m (longitud total ida y vuelta) en vez de 130 m de un sentido. En trifásico eso no aplica: el factor raiz(3) ya considera la geometría del circuito; el factor 2 solo corresponde a circuitos monofásicos.
+Caída de tensión calculada con Tabla 9 (R y XL reales, FP 0.9, raiz(3), 130 m, 10.9 A): 10 AWG = 4.00% | 8 AWG = 2.65% | 6 AWG = 1.70% | 4 AWG = 1.10%.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Sobredimensionamiento de aproximadamente dos calibres respecto al mínimo normativo. NO es una condición insegura (sobra cobre, no falta), pero implica costo adicional de material en ~130 m de recorrido sobre 4 conductores.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente de decisión de César (ing. responsable): aceptar 8 AWG como mínimo normativo, o mantener 4 AWG como decisión consciente de diseño por margen para cargas futuras del alimentador de oficina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="210" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>N-002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Memoria Jardín de Eventos CENTURA — todos los circuitos revisados (C1, AA 5 ton, D).</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>El documento dimensiona el interruptor igualándolo a la ampacidad de tabla del conductor elegido (ej. 8 AWG -&gt; 40 A, 12 AWG -&gt; 20 A), no al siguiente valor estándar por encima de la corriente de diseño.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>El Art. 240-6(a) junto con el 240-4 establecen que la protección se selecciona para la carga real, tomando la ampacidad del conductor como LÍMITE SUPERIOR, no como valor objetivo. Para el circuito C1 (22.7 A de diseño), ElectroNOM selecciona 25 A y el documento 40 A.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Protección más holgada de lo necesario: menor sensibilidad ante sobrecargas sostenidas. Cumple la norma (no excede la ampacidad del conductor) pero no es el criterio literal del Art. 240.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto: César decidió que ElectroNOM se apegue estrictamente a la norma (Art. 240-6(a)/240-4). No se implementó el criterio alterno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="210" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>N-003</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Memoria Jardín de Eventos CENTURA — circuitos con corrección por temperatura.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>El documento mezcla columnas de temperatura: toma la ampacidad base de la columna de 60 °C pero aplica factores de corrección por temperatura de la columna de 75 °C o 90 °C (usa 0.88 y 0.91 para 40 °C).</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>La Tabla 310-15(b)(2)(a) exige que el factor de corrección corresponda a la MISMA temperatura nominal del conductor con la que se tomó la ampacidad base. Para 40 °C: columna 60 °C = 0.82, columna 75 °C = 0.88, columna 90 °C = 0.91.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Inconsistencia interna del documento de referencia. ElectroNOM usa siempre la misma columna para ambos valores, por lo que no reproduce este error.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Informativo: no requiere acción en el software. Útil como criterio de revisión al auditar memorias de terceros.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4240,7 +4240,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de decisión de César (ing. responsable): aceptar 8 AWG como mínimo normativo, o mantener 4 AWG como decisión consciente de diseño por margen para cargas futuras del alimentador de oficina.</t>
+          <t>RESUELTA (8-ago-2026). César, como ingeniero responsable, confirmó que el 4 AWG de la memoria CENTURA fue un ERROR DE CALCULO de ese documento, no una decision de diseno por margen. Criterio adoptado: el minimo normativo correcto para este circuito es 8 AWG (2.65% de caida, dentro del 3%). El calculo de ElectroNOM es el valido.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4151,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sobredimensionamiento de aproximadamente dos calibres respecto al mínimo normativo. NO es una condición insegura (sobra cobre, no falta), pero implica costo adicional de material en ~130 m de recorrido sobre 4 conductores.</t>
+          <t>Sobredimensionamiento de dos calibres en la version de diciembre, ya corregido en la revision de febrero. Sin consecuencia en obra: el proyecto se ejecuto con la revision corregida.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>RESUELTA (8-ago-2026). César, como ingeniero responsable, confirmó que el 4 AWG de la memoria CENTURA fue un ERROR DE CALCULO de ese documento, no una decision de diseno por margen. Criterio adoptado: el minimo normativo correcto para este circuito es 8 AWG (2.65% de caida, dentro del 3%). El calculo de ElectroNOM es el valido.</t>
+          <t>RESUELTA Y CONFIRMADA POR EL PROYECTO. Primero (8-ago-2026) Cesar confirmo que el 4 AWG de la memoria de diciembre fue un ERROR DE CALCULO. Despues, al revisar la REVISION DEL 5-FEB-2026 del mismo proyecto (entregada el 11-ago-2026), resulto que esa revision ya habia corregido el circuito por su cuenta a 8 AWG con interruptor de 15 A: exactamente lo que calcula ElectroNOM. La memoria Rev5 incluso razona igual que la herramienta: 'Verificacion con AWG 10: No cumple (&lt;3%). Verificacion con AWG 8: Cumple'. La revision es de febrero, meses ANTES de este analisis, asi que se trata de una confirmacion independiente: un ingeniero llego por separado al mismo resultado.</t>
         </is>
       </c>
     </row>
@@ -4305,6 +4305,144 @@
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Informativo: no requiere acción en el software. Útil como criterio de revisión al auditar memorias de terceros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="250" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>N-004</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Revision 5-feb-2026 — Alimentador Centro de carga C, tuberia.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>En la version de diciembre la cedula era '3F-4, 1N-4, 1t-8, 1T-1"'. Con 4 conductores de 4 AWG THHN (53.16 mm2 c/u) mas una tierra de 8 AWG (23.61 mm2) suman 236.25 mm2, contra 222 mm2 disponibles al 40% en EMT de 1": ocupacion real 42.6%, por encima del limite.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>El limite de llenado del 40% SI es disposicion obligatoria (Tabla 1, Capitulo 10), a diferencia de la caida de tension que la NOM plantea como NOTA. ElectroNOM calculo 1-1/4" como tuberia minima.
+La revision del 5-feb-2026 ya corrigio la cedula a 1T-1 1/4", que es exactamente lo que calcula la herramienta. Segunda confirmacion independiente en el mismo proyecto.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto en el proyecto antes de este analisis. Confirma que el calculo de llenado de la herramienta detecta correctamente una condicion de incumplimiento obligatorio.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CERRADA. No requiere accion: la revision vigente (5-feb-2026) ya trae 1-1/4".</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="250" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>N-005</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Revision 5-feb-2026 — Conductor de puesta a tierra del Centro de carga D (130 m).</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Tres valores distintos para la misma tierra: la memoria Rev5 dice 14 AWG, el cuadro de cargas Rev5 dice 12 AWG, y ElectroNOM calcula 8 AWG.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>El calibre de fase de ese alimentador se subio de ~14 AWG (que bastaba por ampacidad para 10.83 A) hasta 8 AWG POR CAIDA DE TENSION en 130 m. Eso es un aumento de area de factor ~4.
+El Art. 250-122(b) exige que, cuando los conductores de fase se aumentan por encima del minimo requerido por ampacidad, el conductor de puesta a tierra de equipos se aumente PROPORCIONALMENTE al area. Ambos documentos aplicaron unicamente la tabla del 250-122(a): la memoria lo dice explicitamente ('por criterio tipico de tabla de tierra: PE AWG 14').
+Calculo: area base de tabla para 15 A = 14 AWG (2.08 mm2); factor = 8.37/2.08 = 4.02; area minima de tierra = 2.08 x 4.02 = 8.37 mm2 -&gt; 8 AWG.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Es la regla R-035 del catalogo. Primer caso REAL que confirma que este requisito se escapa en la practica profesional: ni la memoria, ni el cuadro de cargas, ni el motor en Rust del PR #1 lo aplican. Un conductor de tierra subdimensionado compromete la trayectoria de falla.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE de decision de Cesar: confirmar si procede corregir la tierra del CC-D a 8 AWG en el proyecto, o si hay una razon de diseno para mantener el criterio de tabla simple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="250" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>N-006</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Revision 5-feb-2026 — Conflicto entre memoria y cuadro de cargas, Centro de carga B.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Los dos documentos de la MISMA revision no coinciden. Memoria Rev5: 3 x 10 AWG, neutro 10, tierra 10, EMT 3/4", interruptor 30 A. Cuadro de cargas Rev5: '3F-8, 1N-8, 1t-10, 1T-1"', interruptor 40 A.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ElectroNOM calcula 10 AWG con tierra 10 AWG para los 22.7 A demandados: coincide con la MEMORIA. El cuadro de cargas va un calibre por arriba y con interruptor mayor.
+Relacionado: en el Centro de carga C ambos documentos coinciden en 80 A mientras ElectroNOM calcula 60 A. La diferencia ahi es la base de dimensionamiento del interruptor: ellos usan la corriente INSTALADA (73.1 A), la herramienta la DEMANDADA (58.4 A, ya con el factor de 0.8).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>No es una condicion insegura: el cuadro es el documento sobredimensionado. Pero dos documentos de la misma revision con cedulas distintas es un riesgo de ejecucion — en obra se sigue uno u otro.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE de decision de Cesar: definir cual documento manda y unificarlos. Definir tambien si el interruptor se dimensiona sobre carga instalada o demandada (hoy ElectroNOM usa demandada).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="250" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>N-007</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Revision 5-feb-2026 — Cortocircuito con datos reales del transformador (diagrama unifilar DXF).</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Primera validacion del calculo de cortocircuito con datos de un proyecto real: transformador de 300 kVA con %Z = 4.79, dato tomado del diagrama unifilar.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Resultados de ElectroNOM (metodo por unidad, verificado ademas contra la formula directa I_nominal/%Z, ambos dan el mismo valor):
+- Corriente nominal del transformador: 787.3 A
+- Falla trifasica simetrica en el TABLERO PRINCIPAL: 16.44 kA
+- Falla en C.C. B (8 AWG, 10 m): 3.80 kA
+- Falla en C.C. C (4 AWG, 45 m): 2.34 kA
+- Falla en C.C. D (8 AWG, 130 m): 0.37 kA
+Nota de tension: el DXF indica '240V/127' en unos textos y '220/127' en otro, y la memoria usa 220 V. Con 240 V la falla en el principal baja a 15.1 kA. No cambia la conclusion.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Los tableros QO aguas abajo (0.37 a 3.80 kA) quedan holgados con la capacidad interruptiva estandar de 10 kA. Pero en el I-Line principal hay 16.44 kA disponibles, asi que ahi se requieren interruptores de al menos 18 kA (Art. 110-9).</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE de verificacion de Cesar: confirmar que capacidad interruptiva se especifico para los interruptores del tablero principal I-Line, y unificar el dato de tension (220 o 240 V) entre el diagrama unifilar y la memoria.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4408,7 +4408,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="250" customHeight="1">
+    <row r="11" ht="430" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>N-007</t>
@@ -4421,28 +4421,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Primera validacion del calculo de cortocircuito con datos de un proyecto real: transformador de 300 kVA con %Z = 4.79, dato tomado del diagrama unifilar.</t>
+          <t>El proyecto NO CONTIENE ESTUDIO DE CORTOCIRCUITO. Se buscaron menciones de kA, capacidad interruptiva, corriente de falla o cortocircuito en los tres documentos de la revision 5-feb-2026 (memoria tecnica, cuadro de cargas y diagrama unifilar DXF): CERO resultados. El unico numero de catalogo que aparece es QO330L200GRB, sin rating de interrupcion.
+El hallazgo no es que se haya especificado mal un interruptor, sino que la verificacion que exige el Art. 110-9 nunca se hizo.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Resultados de ElectroNOM (metodo por unidad, verificado ademas contra la formula directa I_nominal/%Z, ambos dan el mismo valor):
-- Corriente nominal del transformador: 787.3 A
-- Falla trifasica simetrica en el TABLERO PRINCIPAL: 16.44 kA
-- Falla en C.C. B (8 AWG, 10 m): 3.80 kA
-- Falla en C.C. C (4 AWG, 45 m): 2.34 kA
-- Falla en C.C. D (8 AWG, 130 m): 0.37 kA
-Nota de tension: el DXF indica '240V/127' en unos textos y '220/127' en otro, y la memoria usa 220 V. Con 240 V la falla en el principal baja a 15.1 kA. No cambia la conclusion.</t>
+          <t>Art. 110-9 (texto literal de la NOM-001-SEDE-2018): 'Los equipos destinados a interrumpir corrientes de falla deben tener un rango nominal de interrupcion no menor que la tension nominal del circuito al menos igual a la corriente existente en las terminales de linea del equipo.' Ver tambien Art. 110-10 sobre coordinacion.
+DATO DE PARTIDA (diagrama unifilar): transformador de 300 kVA, %Z = 4.79.
+Corriente nominal del transformador: 787.3 A.
+ANALISIS DE SENSIBILIDAD DE LA FALLA EN EL TABLERO PRINCIPAL:
+  Base (bus infinito, 220 V, %Z 4.79) ....... 16.44 kA
+  Con red de 500 MVA aguas arriba ........... 16.23 kA
+  Con red de 250 MVA ........................ 16.03 kA
+  Con red de 100 MVA ........................ 15.47 kA
+  A 240 V en vez de 220 V ................... 15.07 kA
+  %Z en tolerancia INFERIOR (-7.5%, 4.43) ... 17.77 kA  &lt;-- PEOR CASO CREIBLE
+  %Z en tolerancia superior (+7.5%, 5.15) ... 15.29 kA
+Dos conclusiones del analisis:
+1) La impedancia de la red aguas arriba casi no mueve el resultado (menos de 1 kA en todo el rango de 100 a 500 MVA). No hace falta pedir el nivel de falla a la compania suministradora para tomar la decision.
+2) Lo que si importa es la TOLERANCIA DE FABRICACION del %Z del transformador (tipica +-7.5%): un %Z menor produce MAS falla. Por eso el peor caso creible es 17.77 kA y no 16.44 kA.
+FALLA AGUAS ABAJO (nominal / peor caso):
+  C.C. B (8 AWG, 10 m) .... 3.80 / 3.87 kA
+  C.C. C (4 AWG, 45 m) .... 2.34 / 2.37 kA
+  C.C. D (8 AWG, 130 m) ... 0.37 / 0.37 kA
+Metodo: por unidad, falla trifasica simetrica, sistema radial. Verificado ademas contra la formula directa I_nominal / %Z, que da el mismo valor.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Los tableros QO aguas abajo (0.37 a 3.80 kA) quedan holgados con la capacidad interruptiva estandar de 10 kA. Pero en el I-Line principal hay 16.44 kA disponibles, asi que ahi se requieren interruptores de al menos 18 kA (Art. 110-9).</t>
+          <t>Los tableros aguas abajo estan holgados: con 0.37 a 3.87 kA, cualquier interruptor estandar de 10 kA los cubre con margen amplio. La impedancia del propio alimentador amortigua la falla muy rapido.
+EL PUNTO CRITICO ES EL TABLERO PRINCIPAL I-LINE. Y no es solo su interruptor principal de 400 A: TODOS los interruptores montados en ese tablero ven la falla completa, incluidos los de 3x40, 3x80 y 3x15 que alimentan a los centros de carga B, C y D.
+Un interruptor que intenta interrumpir una falla por encima de su capacidad puede destruirse sin abrir el circuito. Es el unico hallazgo de toda la validacion que toca seguridad y no solo economia de material.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE de verificacion de Cesar: confirmar que capacidad interruptiva se especifico para los interruptores del tablero principal I-Line, y unificar el dato de tension (220 o 240 V) entre el diagrama unifilar y la memoria.</t>
+          <t>PENDIENTE de verificacion de Cesar contra la hoja de datos del fabricante.
+Con 17.77 kA de peor caso, la especificacion minima seria 18 kA, pero con un margen de apenas 1.3%. Lo prudente es 22 kA, la siguiente capacidad comercial.
+QUE FALTA VERIFICAR:
+1) Capacidad interruptiva real del interruptor principal I-Line (modelo LA400M181B segun el cuadro de cargas) y de los interruptores derivados montados en ese mismo tablero. NOTA: los ratings de producto NO se dieron por sabidos en este analisis; deben consultarse en la hoja de datos de Square D.
+2) Unificar el dato de tension: el DXF dice '240V/127' en unos textos y '220/127' en otro, mientras la memoria usa 220 V.
+Lo que SI queda establecido con confianza es la corriente de falla disponible (15 a 18 kA en el principal), que es la mitad del problema.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4450,19 +4450,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Los tableros aguas abajo estan holgados: con 0.37 a 3.87 kA, cualquier interruptor estandar de 10 kA los cubre con margen amplio. La impedancia del propio alimentador amortigua la falla muy rapido.
-EL PUNTO CRITICO ES EL TABLERO PRINCIPAL I-LINE. Y no es solo su interruptor principal de 400 A: TODOS los interruptores montados en ese tablero ven la falla completa, incluidos los de 3x40, 3x80 y 3x15 que alimentan a los centros de carga B, C y D.
-Un interruptor que intenta interrumpir una falla por encima de su capacidad puede destruirse sin abrir el circuito. Es el unico hallazgo de toda la validacion que toca seguridad y no solo economia de material.</t>
+          <t>RESUELTO EN CUANTO A SEGURIDAD. Con el rating real del equipo (ver columna Estado), el margen es amplio en todos los puntos de la instalacion:
+  Tablero principal I-Line ... 17.77 kA disponibles contra 42 kA de capacidad = margen 2.4x
+  Interruptores derivados .... 17.77 kA contra 25 kA minimo del marco H = cumple
+  Tableros QO aguas abajo .... 0.37 a 3.87 kA contra 10 kA estandar = sobrado
+LO QUE SI QUEDA COMO HALLAZGO: el estudio no esta documentado. El equipo cumple, pero la memoria no contiene ningun calculo de cortocircuito ni menciona capacidad interruptiva. Para efectos de verificacion (p. ej. si una UVIE lo solicita), el cumplimiento del Art. 110-9 debe poder DEMOSTRARSE, no solo darse por hecho. Es un ajuste de memoria tecnica, no de obra.
+Nota de metodo: el punto de exposicion no es solo el interruptor principal. TODOS los interruptores montados en el tablero principal ven la falla completa, incluidos los derivados que alimentan a los centros de carga B, C y D.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE de verificacion de Cesar contra la hoja de datos del fabricante.
-Con 17.77 kA de peor caso, la especificacion minima seria 18 kA, pero con un margen de apenas 1.3%. Lo prudente es 22 kA, la siguiente capacidad comercial.
-QUE FALTA VERIFICAR:
-1) Capacidad interruptiva real del interruptor principal I-Line (modelo LA400M181B segun el cuadro de cargas) y de los interruptores derivados montados en ese mismo tablero. NOTA: los ratings de producto NO se dieron por sabidos en este analisis; deben consultarse en la hoja de datos de Square D.
-2) Unificar el dato de tension: el DXF dice '240V/127' en unos textos y '220/127' en otro, mientras la memoria usa 220 V.
-Lo que SI queda establecido con confianza es la corriente de falla disponible (15 a 18 kA en el principal), que es la mitad del problema.</t>
+          <t>CERRADA (11-ago-2026), con hallazgo documental abierto.
+RATING VERIFICADO contra la hoja de datos del fabricante (Schneider Electric, tableros I-Line Serie B, catalogo SCHC180, tabla de capacidad de interrupcion):
+  Marco LA, 2-3 polos, TM, rango 125-400 A:
+     240 V -&gt; 42 kA simetricos
+     480 V -&gt; 30 kA
+     600 V -&gt; 22 kA
+El LA400M181B es un tablero I-Line con interruptor principal de marco LA, por lo que a 240 V (columna que cubre el sistema de 220 V) su capacidad es de 42 kA contra los 17.77 kA del peor caso: CUMPLE el Art. 110-9 con margen de 2.4x.
+Derivados: la misma hoja indica que el tablero tamano 1 admite derivados de hasta 250 A en marcos H y J. El mas bajo de esa familia (HDA) es de 25 kA a 240 V, tambien por encima de los 17.77 kA. Los numeros de catalogo especificos de los derivados no aparecen en los documentos del proyecto, pero cualquier opcion compatible con ese tablero cumple.
+PENDIENTES MENORES:
+1) Incorporar el estudio de cortocircuito a la memoria tecnica, aunque el resultado sea favorable.
+2) Unificar el dato de tension: el DXF dice '240V/127' en unos textos y '220/127' en otro, mientras la memoria usa 220 V.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4375,7 +4375,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="250" customHeight="1">
+    <row r="10" ht="400" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>N-006</t>
@@ -4393,18 +4393,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ElectroNOM calcula 10 AWG con tierra 10 AWG para los 22.7 A demandados: coincide con la MEMORIA. El cuadro de cargas va un calibre por arriba y con interruptor mayor.
-Relacionado: en el Centro de carga C ambos documentos coinciden en 80 A mientras ElectroNOM calcula 60 A. La diferencia ahi es la base de dimensionamiento del interruptor: ellos usan la corriente INSTALADA (73.1 A), la herramienta la DEMANDADA (58.4 A, ya con el factor de 0.8).</t>
+          <t>RECALCULO CON EL MOTOR CORREGIDO (Art. 110-14(c) y tipo de aislamiento), aplicando el criterio de CARGA CONTINUA que la propia memoria invoca ('Interruptor (criterio tipico de carga continua)'):
+  Corriente demandada .......... 22.86 A
+  Requerida con 125% (210-19) .. 28.58 A
+  Calibre ...................... 10 AWG
+  Interruptor .................. 30 A
+Coincide EXACTAMENTE con la memoria (10 AWG / 30 A). La memoria aplico bien el 125% del Art. 210-19 y el resultado es el minimo normativo correcto. El 8 AWG / 40 A del cuadro es la version sobredimensionada, con el interruptor igualado a la ampacidad del conductor (mismo patron de N-002).
+PERO EL MARGEN ES DE NAVAJA:
+  Ampacidad utilizable del 10 AWG .. 29.12 A
+  Requerida ........................ 28.58 A
+  Margen ........................... 0.54 A = 1.85%
+Punto donde se voltea el calibre (misma configuracion, variando la carga instalada):
+  9,800 W (el proyecto) .. 10 AWG
+  9,950 W ................ 10 AWG
+  9,990 W ................ 8 AWG   &lt;-- se voltea aqui
+  10,100 W ............... 8 AWG
+Un aumento de 1.9% en la carga tumba el 10 AWG. En terminos practicos, agregar UN contacto de 200 VA a ese centro de carga ya obliga a subir de calibre. Y ese tablero alimenta fuerza de terraza, alberca y banos: un area donde agregar cargas es probable.
+Nota: declarar el equipo marcado para 75 C NO ayuda en este caso. El tope de terminal sube a 35 A, pero manda la ampacidad corregida de 29.12 A, que no cambia.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>No es una condicion insegura: el cuadro es el documento sobredimensionado. Pero dos documentos de la misma revision con cedulas distintas es un riesgo de ejecucion — en obra se sigue uno u otro.</t>
+          <t>Ninguno de los dos documentos esta equivocado: la memoria calculo el minimo normativo correctamente, y el cuadro eligio el calibre que sobrevive a cualquier crecimiento pequeno. Ambos son defendibles.
+LO QUE SI ES UN PROBLEMA REAL es que NO COINCIDEN. En obra se sigue un documento u otro, y ahi la discrepancia si tiene consecuencia.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE de decision de Cesar: definir cual documento manda y unificarlos. Definir tambien si el interruptor se dimensiona sobre carga instalada o demandada (hoy ElectroNOM usa demandada).</t>
+          <t>RESUELTA (12-ago-2026). Decision de Cesar: UNIFICAR HACIA 8 AWG.
+Razon: el 10 AWG es el minimo normativo correcto, pero deja apenas 1.85% de margen. Un aumento de 1.9% en la carga lo saca de norma, y el centro de carga B alimenta un area propensa a ampliaciones (terraza, alberca, banos). El 8 AWG cuesta poco mas en 10 m de recorrido y elimina ese riesgo.
+ACCION PENDIENTE EN EL PROYECTO: corregir la MEMORIA TECNICA para que diga 8 AWG, de modo que coincida con el cuadro de cargas (que ya trae 8 AWG). El cuadro no se toca.
+CRITERIO GENERAL QUE DEJA ESTA NOTA: cuando el calibre minimo quede con menos de ~5% de margen sobre la ampacidad utilizable, conviene subir al siguiente calibre en vez de apurar el minimo, sobre todo en tableros con probabilidad de ampliacion. No es requisito normativo, es criterio de diseno.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4341,7 +4341,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="250" customHeight="1">
+    <row r="9" ht="400" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>N-005</t>
@@ -4359,19 +4359,33 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>El calibre de fase de ese alimentador se subio de ~14 AWG (que bastaba por ampacidad para 10.83 A) hasta 8 AWG POR CAIDA DE TENSION en 130 m. Eso es un aumento de area de factor ~4.
-El Art. 250-122(b) exige que, cuando los conductores de fase se aumentan por encima del minimo requerido por ampacidad, el conductor de puesta a tierra de equipos se aumente PROPORCIONALMENTE al area. Ambos documentos aplicaron unicamente la tabla del 250-122(a): la memoria lo dice explicitamente ('por criterio tipico de tabla de tierra: PE AWG 14').
-Calculo: area base de tabla para 15 A = 14 AWG (2.08 mm2); factor = 8.37/2.08 = 4.02; area minima de tierra = 2.08 x 4.02 = 8.37 mm2 -&gt; 8 AWG.</t>
+          <t>CONFIRMADO CON EL MOTOR CORREGIDO (14-ago-2026, tras implementar Art. 110-14(c) y tipo de aislamiento). El recalculo no cambia la conclusion original:
+  Corriente demandada .......................... 10.82 A
+  Calibre minimo por ampacidad (circuito 15 A) .. 14 AWG
+  Caida de tension con 14 AWG a 130 m ........... 4.7% (excede el 3%)
+  Calibre final (sube por caida de tension) ..... 8 AWG
+  Interruptor .................................... 15 A
+MECANICA DEL HALLAZGO (Art. 250-122b):
+1) La fase minima por ampacidad seria 14 AWG (el interruptor de 15 A no exige mas).
+2) Pero a 130 m, 14 AWG da 4.7% de caida de tension, muy por encima del 3% -&gt; se sube a 8 AWG.
+3) El Art. 250-122(b) exige que si la fase se aumenta por encima del minimo por ampacidad, la tierra se aumente PROPORCIONALMENTE AL AREA. Factor = area(8 AWG)/area(14 AWG) = 4.02.
+4) Aplicando el factor a la base de tabla (14 AWG, correspondiente a interruptor de 15 A): area(14 AWG) x 4.02 -&gt; calibre resultante 8 AWG.
+Ni la memoria (14 AWG) ni el cuadro (12 AWG) dan ese paso: ambos se quedan en la Tabla 250-122(a) simple, que solo mira la capacidad del interruptor. Eso es correcto SOLO cuando la fase no se movio del minimo por ampacidad -- aqui si se movio, y bastante (factor 4x).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Es la regla R-035 del catalogo. Primer caso REAL que confirma que este requisito se escapa en la practica profesional: ni la memoria, ni el cuadro de cargas, ni el motor en Rust del PR #1 lo aplican. Un conductor de tierra subdimensionado compromete la trayectoria de falla.</t>
+          <t>A diferencia de N-006 (donde el problema era economico: dos calibres validos, uno con poco margen), AQUI SI HAY UN INCUMPLIMIENTO REAL. 14 AWG de tierra no es una opcion normativa valida para este alimentador: es un conductor de puesta a tierra subdimensionado frente al Art. 250-122(b).
+Un conductor de tierra subdimensionado compromete la trayectoria de despeje de falla: en caso de una falla a tierra, el conductor debe soportar la corriente de falla el tiempo suficiente para que actue la proteccion, sin fundirse ni generar un riesgo de choque electrico en las partes metalicas del equipo. Con 130 m de recorrido, un conductor angosto ademas tiene mayor impedancia, lo que retarda el disparo de la proteccion.
+Es el primer caso real (fuera de este proyecto) que confirma que el aumento proporcional del 250-122(b) se escapa en la practica profesional: ni la memoria, ni el cuadro de cargas, ni el motor en Rust del PR #1 lo aplican.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE de decision de Cesar: confirmar si procede corregir la tierra del CC-D a 8 AWG en el proyecto, o si hay una razon de diseno para mantener el criterio de tabla simple.</t>
+          <t>CERRADA (14-ago-2026). Confirmado: el calibre correcto de tierra para el C.C. D es 8 AWG.
+ACCION PENDIENTE EN EL PROYECTO (no realizada por esta herramienta -- son documentos de responsiva de Cesar): corregir tanto la memoria tecnica (14 AWG -&gt; 8 AWG) como el cuadro de cargas (12 AWG -&gt; 8 AWG) del Centro de carga D, para que el conductor de puesta a tierra cumpla el Art. 250-122(b).
+CRITERIO GENERAL QUE DEJA ESTA NOTA: siempre que un alimentador suba de calibre de fase por caida de tension (no solo por ampacidad), verificar el conductor de tierra con el factor proporcional del 250-122(b) en vez de tomar directamente la Tabla 250-122(a). Es el punto donde la practica comun tiende a fallar, segun esta validacion.
+Con esto se cierran las 7 notas de validacion registradas (N-001 a N-007) contra el proyecto CENTURA.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4151,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4507,6 +4507,50 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>N-008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Memoria Tecnica Advanced Energy Planta 3 (10-abr-2026) — Alimentadores de Transformadores 03/04/05 (2500 kVA c/u, Delta-Estrella, 34.5kV/480-277V) a tablero SWBD 3000A, 8 conductores 500 kcmil de cobre en paralelo por fase, 8 m.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Memoria Tecnica Advanced Energy Planta 3 (10-abr-2026, proyecto de media tension industrial) se uso UNICAMENTE COMO APOYO para validar el motor de calculo de ElectroNOM, por instruccion expresa de Cesar: el software se acota a BAJA TENSION (Titulo 5 de la NOM, menor a 1000 V). El proyecto Advanced Energy no es un requerimiento de alcance, es solo material de prueba.
+Se validaron dos calculos contra la memoria real (3 transformadores de 2500 kVA, Delta-Estrella, 34.5kV/480-277V, alimentando un tablero SWBD 3000A a 8 m mediante 8 conductores 500 kcmil de cobre en paralelo por fase):
+1) CAIDA DE TENSION: la memoria reporta 0.16% (500 kcmil, 8 m, 480 V). Con la formula de impedancia de ElectroNOM (Tabla 9: r=0.089, x=0.128 Ohm/km) y la corriente por conductor (375.89 A = 3007.12/8), el resultado coincide (0.1606%) solo asumiendo FP=0.8. La memoria no declara el FP usado en esa seccion especifica del documento extraido.
+2) CORTOCIRCUITO AGUAS ABAJO EN EL SWBD: la memoria usa el metodo punto-a-punto (C-value / Bussmann). ElectroNOM usa el metodo por unidad. calcularCortocircuito() no soporta conductores en paralelo nativamente, asi que se extendio manualmente (impedancia del conductor / 8) para la comparacion:
+   T03 (%Z 6.61): memoria 44.41 kA vs ElectroNOM 44.35 kA (dif. 0.14%)
+   T04 (%Z 6.72): memoria 43.70 kA vs ElectroNOM 43.66 kA (dif. 0.09%)
+   T05 (%Z 6.60): memoria 44.48 kA vs ElectroNOM 44.42 kA (dif. 0.13%)
+Coinciden dentro del margen de redondeo esperado: los dos metodos son matematicamente equivalentes.
+3) HIPOTESIS DESCARTADA (metros vs pies): el metodo punto-a-punto original (Bussmann/IEEE) usa tablas de valor C calibradas para longitud en PIES. La memoria usa L=8 directamente como METROS (mismo valor que en la caida de tension). Se probo la hipotesis de que fuera un error de unidades: si lo fuera, el calculo metrico-nativo de ElectroNOM (Tabla 9 en Ohm/km) debia dar un resultado muy distinto al de la memoria. No fue asi (coincidencia dentro de 0.15%), asi que la tabla 'Cuadro 17' de la memoria ya esta adaptada a metros. NO hay error de unidades en el documento.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Confirma que el motor de ElectroNOM (calcularCaidaTension y calcularCortocircuito, metodo por unidad) produce resultados correctos y consistentes con un metodo independiente (punto-a-punto) usado en un tercer proyecto real, fuera de la familia de documentos CENTURA.
+BRECHA DE CAPACIDAD CONFIRMADA (no es un error, es una funcionalidad ausente): calcularCortocircuito() no admite multiples conductores en paralelo por fase (Art. 310-10(h)). Para reproducir el calculo de Advanced Energy fue necesario dividir la impedancia manualmente fuera de la funcion. Los conductores en paralelo SI son un tema de baja tension (aplica en Titulo 5 tambien, no es exclusivo de media tension), asi que esta brecha sigue vigente independientemente del acotamiento de alcance.
+DECISION DE ALCANCE (instruccion expresa de Cesar, 15-ago-2026): ElectroNOM se mantiene acotado a BAJA TENSION (Titulo 5, menor a 1000 V). Todo lo de media tension que aparece en la memoria de Advanced Energy (cuchillas fusibles 34.5kV, apartarrayos, transformadores tipo estacion, Titulo 6/Capitulo 9) queda explicitamente FUERA DE ALCANCE y no se debe implementar. El documento se usa solo como material de validacion del motor de calculo en la parte que SI es baja tension (el alimentador del secundario del transformador hacia el tablero, 480V).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ninguna correccion requerida en el motor de calculo: los dos metodos (por unidad vs punto-a-punto) coinciden. No se hacen cambios de alcance hacia media tension.
+Queda registrado como mejora pendiente (no urgente, no solicitada aun): agregar soporte de conductores en paralelo a calcularCortocircuito() y calcularCaidaTension() para proyectos de baja tension con alimentadores grandes que usan varios conductores por fase.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CERRADA / INFORMATIVA (15-ago-2026). El motor de calculo queda validado contra un tercer proyecto real. Alcance de ElectroNOM confirmado y documentado: solo baja tension (Titulo 5, &lt;1000V). Advanced Energy Planta 3 se usa unicamente como material de prueba, no como driver de nuevas funcionalidades de media tension.
+PENDIENTE ABIERTO (separado de esta nota, sujeto a decision futura de Cesar): soporte de conductores en paralelo por fase en el motor de cortocircuito y caida de tension.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4151,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4507,6 +4507,53 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>N-009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Memoria PIE-2026-003 VERTIV (22-abr-2026, Rev.1) — Alimentadores de generadores QSK60 (1,300 kW c/u, 480V/60Hz) al tablero colector de baja tension, 6 conductores 500 kcmil de cobre en paralelo por fase, 30 m, charola portacable tipo escalera.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Memoria de Calculo de Conductores Electricos PIE-2026-003 (VERTIV, Central de Generacion y Centro de Carga en Abasto Aislado, 22-abr-2026, Rev.1) — generadores gas natural QSK60, 1,300 kW c/u, 480V/60Hz, FP 0.8. A diferencia de Advanced Energy (N-008), este proyecto SI es baja tension (Titulo 5), por lo que aplica como material de validacion de pleno derecho, no solo como apoyo.
+COINCIDENCIAS CONFIRMADAS (2):
+1) CAIDA DE TENSION con conductores en paralelo: 6 conductores 500 kcmil de cobre por fase, 30 m, In=1,954.63 A, FP 0.8. La memoria reporta e%=0.56707%. Aplicando la formula de impedancia de ElectroNOM (calcularCaidaTension, Tabla 9: r=0.105, x=0.128 Ohm/km) con la corriente dividida entre los 6 conductores (325.77 A c/u), el resultado es 0.5669% -- coincide dentro del redondeo esperado. Segunda confirmacion independiente (la primera fue N-008 con Advanced Energy) de que dividir corriente/impedancia entre el numero de conductores en paralelo reproduce el metodo real usado en campo.
+2) CONDUCTOR DE PUESTA A TIERRA: con interruptor de 2,500 A (ajuste de tiempo largo), la memoria usa la Tabla 250-122(a) y obtiene 350 kcmil de cobre (177 mm2) como area minima requerida (suben a 500 kcmil por disponibilidad comercial, no por norma). La tabla GROUND_TABLE_250_122 de ElectroNOM tiene exactamente esa fila: maxBreaker 2500 -&gt; cu 350. Coincidencia exacta.
+CAPACIDADES AUSENTES EN ELECTRONOM CONFIRMADAS (3, todas dentro de alcance de baja tension, no se pudo validar por falta de la funcionalidad, no por error):
+3) Ampacidad en charola portacable (Tabla 310-15(b)(17) + Art. 392-80(a)(2)(b) para charola cubierta, 60% de derateo sobre la ampacidad al aire libre). ElectroNOM solo implementa la Tabla 310-15(b)(16) (tuberia/canalizacion cerrada). Son tablas y metodos de instalacion distintos.
+4) Verificacion termica del conductor ante cortocircuito (formula adiabatica I^2/A^2 * t = 0.0297 * log10[(T2+234)/(T1+234)], que da el area minima de cobre para soportar la energia de falla sin danar el aislamiento). ElectroNOM solo verifica que el INTERRUPTOR tenga capacidad interruptiva suficiente (Art. 110-9); no verifica si el conductor mismo sobrevive el calentamiento de la falla.
+5) Llenado de charola portacable (Art. 392-22). ElectroNOM solo calcula llenado de tuberia (conduit).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Confirma, en un TERCER proyecto real y esta vez enteramente de baja tension, que:
+- El metodo de caida de tension de ElectroNOM (Tabla 9, formula de impedancia) es correcto tambien para alimentadores con multiples conductores en paralelo, si se divide la corriente entre el numero de conductores.
+- La Tabla 250-122(a) implementada en GROUND_TABLE_250_122 es correcta hasta al menos 2,500 A de proteccion.
+Identifica tres capacidades de baja tension ausentes (charola portacable para ampacidad, verificacion termica del conductor ante falla, llenado de charola). Ninguna es un error del motor: son calculos que la NOM contempla (Art. 392 para charola, formula adiabatica estandar para verificacion termica) pero que ElectroNOM no implementa todavia porque hasta ahora todos los proyectos de validacion usaban tuberia (conduit), no charola, y ninguno tenia corrientes de falla lo bastante altas para que la verificacion termica del conductor fuera el factor limitante en vez de la capacidad del interruptor.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ninguna correccion requerida en el motor de calculo existente: las dos verificaciones que si se pudieron comparar (caida de tension con conductores en paralelo, tierra por Tabla 250-122a) coinciden con la memoria real.
+Quedan registradas como mejoras pendientes (no urgentes, sujetas a priorizacion de Cesar):
+  a) Ampacidad para instalacion en charola portacable (Tabla 310-15(b)(17) + derateos del Art. 392).
+  b) Verificacion termica (I^2t) del conductor de fase ante corriente de cortocircuito.
+  c) Llenado de charola portacable (Art. 392-22).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CERRADA / INFORMATIVA (18-ago-2026). Motor de calculo validado por tercera vez en un proyecto real, esta vez de baja tension pura. Caida de tension con conductores en paralelo y tabla de tierra 250-122(a) confirmadas exactas.
+PENDIENTES ABIERTOS (separados de esta nota, sujetos a decision futura de Cesar sobre prioridad): soporte de ampacidad en charola portacable, verificacion termica del conductor ante cortocircuito, y llenado de charola portacable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2132,6 +2132,48 @@
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>R-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>310-10(h)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Conductores en paralelo por fase</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>El circuito o alimentador usa mas de un conductor por fase para dividir la corriente (tipico en alimentadores grandes: transformadores, generadores, tableros principales).</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cada conductor de fase debe ser del mismo material, calibre (area transversal), tipo de aislamiento y longitud que los demas, e ir en el mismo tipo de canalizacion (o disposicion equivalente si van al aire libre), y terminar de forma similar en ambos extremos. El calibre se selecciona para que UN conductor lleve la fraccion de corriente que le corresponde (corriente total / numero de conductores en paralelo); la caida de tension y el cortocircuito se calculan repartiendo corriente/impedancia entre el numero de conductores.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Memoria con: numero de conductores en paralelo por fase, calibre y longitud de cada uno, y confirmacion de que son identicos entre si.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 310-10(h)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>
@@ -4176,6 +4218,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -4564,12 +4607,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Memoria de Calculo de Conductores Electricos PIE-2026-003 (VERTIV, Central de Generacion y Centro de Carga en Abasto Aislado, 22-abr-2026, Rev.1) — generadores gas natural QSK60, 1,300 kW c/u, 480V/60Hz, FP 0.8. A diferencia de Advanced Energy (N-008), este proyecto SI es baja tension (Titulo 5), por lo que aplica como material de validacion de pleno derecho, no solo como apoyo.
-COINCIDENCIAS CONFIRMADAS (2):
-1) CAIDA DE TENSION con conductores en paralelo: 6 conductores 500 kcmil de cobre por fase, 30 m, In=1,954.63 A, FP 0.8. La memoria reporta e%=0.56707%. Aplicando la formula de impedancia de ElectroNOM (calcularCaidaTension, Tabla 9: r=0.105, x=0.128 Ohm/km) con la corriente dividida entre los 6 conductores (325.77 A c/u), el resultado es 0.5669% -- coincide dentro del redondeo esperado. Segunda confirmacion independiente (la primera fue N-008 con Advanced Energy) de que dividir corriente/impedancia entre el numero de conductores en paralelo reproduce el metodo real usado en campo.
-2) CONDUCTOR DE PUESTA A TIERRA: con interruptor de 2,500 A (ajuste de tiempo largo), la memoria usa la Tabla 250-122(a) y obtiene 350 kcmil de cobre (177 mm2) como area minima requerida (suben a 500 kcmil por disponibilidad comercial, no por norma). La tabla GROUND_TABLE_250_122 de ElectroNOM tiene exactamente esa fila: maxBreaker 2500 -&gt; cu 350. Coincidencia exacta.
+          <t>Memoria de Calculo de Conductores Electricos PIE-2026-003 (VERTIV, Central de Generacion y Centro de Carga en Abasto Aislado, 22-abr-2026, Rev.1) -- generadores gas natural QSK60, 1,300 kW c/u, 480V/60Hz, FP 0.8. A diferencia de Advanced Energy (N-008), este proyecto SI es baja tension (Titulo 5), por lo que aplica como material de validacion de pleno derecho, no solo como apoyo.
+CORRECCION (18-ago-2026): la version original de esta nota afirmaba que la caida de tension coincidia "exacto" con ElectroNOM usando "Tabla 9: r=0.105, x=0.128". Eso fue un ERROR: 0.105 es el valor de R que reporta LA MEMORIA de VERTIV, no el valor real de la Tabla 9 de ElectroNOM (TABLE9_PVC_CU en motor.js tiene r=0.089 ohm/km para 500 kcmil). Se detecto al escribir las pruebas automatizadas de la funcionalidad de conductores en paralelo (ver mas abajo) y se corrige aqui de forma transparente. El hallazgo real es el siguiente:
+1) CAIDA DE TENSION con conductores en paralelo: 6 conductores 500 kcmil de cobre por fase, 30 m, In=1,954.63 A, FP 0.8. La memoria reporta e%=0.56707% usando su propio valor de R=0.105 ohm/km. Llamando a calcularCaidaTension('500', 1954.63, 30, 480, raiz(3), 0.8, 6) -- es decir, con el R REAL de la Tabla 9 de ElectroNOM (r=0.089 ohm/km, X=0.128 ohm/km) -- el resultado es 0.52%, NO 0.567%. Diferencia de ~0.045 puntos porcentuales (~8% relativo). Ambos valores estan comodamente bajo el 3% de la NOM, asi que no hay impacto de seguridad, pero NO es el "match exacto" que se afirmo originalmente.
+CAUSA PROBABLE: la instalacion de VERTIV es CHAROLA PORTACABLE (charola), mientras que la Tabla 9 de ElectroNOM (TABLE9_PVC_CU) es especificamente para conductores en TUBERIA PVC (ver comentario en motor.js). La NOM-001 Tabla 9 real trae columnas de R distintas segun el tipo de canalizacion (PVC, aluminio, acero, etc.), y ElectroNOM no tiene la columna de charola/al aire libre. Esto no es un hallazgo nuevo: es la MISMA brecha ya documentada en el punto 3 de esta nota (ampacidad en charola), que ahora se confirma que tambien afecta la caida de tension, no solo la ampacidad.
+LO QUE SI SE VALIDA con este caso: la ARITMETICA de repartir corriente/impedancia entre N conductores en paralelo (dividir la corriente entre N dentro de calcularCaidaTension) es correcta -- si se le da a la formula el mismo R que uso la memoria, reproduce su 0.567% (verificado a mano). El desajuste esta exclusivamente en el origen del valor de R (tabla de PVC vs. charola), no en la logica de conductores en paralelo agregada a ElectroNOM.
+2) CONDUCTOR DE PUESTA A TIERRA: con interruptor de 2,500 A (ajuste de tiempo largo), la memoria usa la Tabla 250-122(a) y obtiene 350 kcmil de cobre (177 mm2) como area minima requerida (suben a 500 kcmil por disponibilidad comercial, no por norma). La tabla GROUND_TABLE_250_122 de ElectroNOM tiene exactamente esa fila: maxBreaker 2500 -&gt; cu 350. Coincidencia exacta. Este punto NO cambia con la correccion: no depende de la Tabla 9 ni de R/X.
 CAPACIDADES AUSENTES EN ELECTRONOM CONFIRMADAS (3, todas dentro de alcance de baja tension, no se pudo validar por falta de la funcionalidad, no por error):
-3) Ampacidad en charola portacable (Tabla 310-15(b)(17) + Art. 392-80(a)(2)(b) para charola cubierta, 60% de derateo sobre la ampacidad al aire libre). ElectroNOM solo implementa la Tabla 310-15(b)(16) (tuberia/canalizacion cerrada). Son tablas y metodos de instalacion distintos.
+3) Ampacidad en charola portacable (Tabla 310-15(b)(17) + Art. 392-80(a)(2)(b) para charola cubierta, 60% de derateo sobre la ampacidad al aire libre). ElectroNOM solo implementa la Tabla 310-15(b)(16) (tuberia/canalizacion cerrada). Son tablas y metodos de instalacion distintos. (Ahora confirmado que esta misma brecha tambien explica la diferencia de R en la caida de tension del punto 1.)
 4) Verificacion termica del conductor ante cortocircuito (formula adiabatica I^2/A^2 * t = 0.0297 * log10[(T2+234)/(T1+234)], que da el area minima de cobre para soportar la energia de falla sin danar el aislamiento). ElectroNOM solo verifica que el INTERRUPTOR tenga capacidad interruptiva suficiente (Art. 110-9); no verifica si el conductor mismo sobrevive el calentamiento de la falla.
 5) Llenado de charola portacable (Art. 392-22). ElectroNOM solo calcula llenado de tuberia (conduit).</t>
         </is>
@@ -4577,24 +4622,27 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>Confirma, en un TERCER proyecto real y esta vez enteramente de baja tension, que:
-- El metodo de caida de tension de ElectroNOM (Tabla 9, formula de impedancia) es correcto tambien para alimentadores con multiples conductores en paralelo, si se divide la corriente entre el numero de conductores.
+- La ARITMETICA de conductores en paralelo (dividir corriente e impedancia entre N) implementada en calcularCaidaTension y calcularCortocircuito es correcta.
 - La Tabla 250-122(a) implementada en GROUND_TABLE_250_122 es correcta hasta al menos 2,500 A de proteccion.
-Identifica tres capacidades de baja tension ausentes (charola portacable para ampacidad, verificacion termica del conductor ante falla, llenado de charola). Ninguna es un error del motor: son calculos que la NOM contempla (Art. 392 para charola, formula adiabatica estandar para verificacion termica) pero que ElectroNOM no implementa todavia porque hasta ahora todos los proyectos de validacion usaban tuberia (conduit), no charola, y ninguno tenia corrientes de falla lo bastante altas para que la verificacion termica del conductor fuera el factor limitante en vez de la capacidad del interruptor.</t>
+- (CORREGIDO) El valor de R de la Tabla 9 de ElectroNOM (para PVC conduit) NO reproduce exactamente la caida de tension de un proyecto en charola portacable, porque son canalizaciones distintas con R distinta segun la NOM. Esto no es un error de formula: es la brecha de charola ya identificada (punto 3) manifestandose tambien en caida de tension.
+Identifica tres capacidades de baja tension ausentes (charola portacable para ampacidad Y caida de tension, verificacion termica del conductor ante falla, llenado de charola). Ninguna es un error del motor: son calculos que la NOM contempla pero que ElectroNOM no implementa todavia.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ninguna correccion requerida en el motor de calculo existente: las dos verificaciones que si se pudieron comparar (caida de tension con conductores en paralelo, tierra por Tabla 250-122a) coinciden con la memoria real.
+          <t>Ninguna correccion requerida en el motor de calculo existente para el caso de tuberia PVC (la unica canalizacion que ElectroNOM modela hoy). La logica de conductores en paralelo agregada a calcularCaidaTension y calcularCortocircuito queda validada.
+El conductor de tierra por Tabla 250-122(a) coincide con la memoria real, sin cambios.
 Quedan registradas como mejoras pendientes (no urgentes, sujetas a priorizacion de Cesar):
-  a) Ampacidad para instalacion en charola portacable (Tabla 310-15(b)(17) + derateos del Art. 392).
+  a) Ampacidad Y caida de tension para instalacion en charola portacable (Tabla 310-15(b)(17)/Tabla 9 charola + derateos del Art. 392).
   b) Verificacion termica (I^2t) del conductor de fase ante corriente de cortocircuito.
   c) Llenado de charola portacable (Art. 392-22).</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CERRADA / INFORMATIVA (18-ago-2026). Motor de calculo validado por tercera vez en un proyecto real, esta vez de baja tension pura. Caida de tension con conductores en paralelo y tabla de tierra 250-122(a) confirmadas exactas.
-PENDIENTES ABIERTOS (separados de esta nota, sujetos a decision futura de Cesar sobre prioridad): soporte de ampacidad en charola portacable, verificacion termica del conductor ante cortocircuito, y llenado de charola portacable.</t>
+          <t>CERRADA / INFORMATIVA, CON CORRECCION (18-ago-2026). Motor de calculo validado por tercera vez en un proyecto real de baja tension. Conductor de tierra (250-122a) y aritmetica de conductores en paralelo confirmados correctos. La afirmacion original de "match exacto" en caida de tension fue un error de esta nota (se uso el R de la memoria en vez del R real de motor.js) y queda corregida arriba: la diferencia observada (0.52% calculado vs 0.567% de la memoria) se explica por la brecha ya conocida de charola portacable, no por un defecto en la formula.
+PENDIENTES ABIERTOS (separados de esta nota, sujetos a decision futura de Cesar sobre prioridad): soporte de ampacidad y caida de tension en charola portacable, verificacion termica del conductor ante cortocircuito, y llenado de charola portacable.
+FUNCIONALIDAD IMPLEMENTADA (PR conductores en paralelo, 18-ago-2026): calcularCaidaTension y calcularCortocircuito ahora aceptan un parametro nParalelo (Art. 310-10(h)); calcularCalibre se llama con la ampacidad requerida dividida entre nParalelo desde index.html. Nueva regla R-039 en el catalogo. Ver electronom/motor.js y electronom/pruebas.html.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2174,48 @@
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>R-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>110-10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Verificacion termica del conductor ante cortocircuito</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Se calculo la corriente de cortocircuito en el extremo de la carga (seccion de cortocircuito activada, con longitud y calibre validos en Tabla 9) y se declaro el tiempo de despeje de la falla segun la curva tiempo-corriente del dispositivo de proteccion. Solo implementado para cobre.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>El area minima del conductor (formula adiabatica de Onderdonk / ICEA P-32-382: (I/A)^2 * t = 0.0297 * log10[(T2+234)/(T1+234)], con T1 = temperatura nominal del aislamiento y T2 = temperatura maxima admisible durante la falla) no debe exceder el area realmente instalada, dividiendo la corriente entre el numero de conductores en paralelo si aplica.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Memoria con: corriente de falla usada, tiempo de despeje declarado (y su origen, ej. curva del interruptor/fusible), temperaturas T1/T2 usadas, area minima calculada y area instalada.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 110-10 (caracteristicas de cortocircuito de los componentes). La formula en si es de ingenieria general (ICEA P-32-382 / IEEE Std 242), no una tabla de la NOM.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>
@@ -4218,7 +4260,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2216,6 +2216,48 @@
         </is>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>392-22(b)(1)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Llenado de charola portacable (cables de un solo conductor)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>El metodo de instalacion elegido es charola portacable tipo escalera, malla o fondo ventilado (no fondo solido), con cables de un solo conductor (no cable multiconductor) de calibre 250 a 900 kcmil (127 a 456 mm2).</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>La suma de las areas transversales de los conductores aislados (fases + neutro + tierra, si aplica) no debe exceder el area de ocupacion maxima permisible de la Tabla 392-22(b)(1), columna 1, para el ancho interior de charola elegido.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Memoria con: area total de conductores, ancho de charola elegido y area disponible segun la tabla.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 392-22(b)(1)(b), Tabla 392-22(b)(1).</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2258,48 @@
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>R-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>220-54</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Factor de demanda de secadoras domesticas de ropa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Vivienda con dos o mas secadoras electricas de ropa domesticas conectadas al mismo alimentador.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aplicar el factor de demanda de la Tabla 220-54 segun la cantidad de secadoras (100% de 1 a 4, y decreciente de 5 en adelante: 85, 75, 65, 60, 55, 50, 47% para 5 a 11 secadoras; mas de 11 usa una formula distinta). La carga base por secadora es la mayor entre 5000 VA y la de la placa de datos.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Memoria con: cantidad de secadoras, VA por secadora (placa vs minimo de 5000), factor de demanda aplicado segun la Tabla 220-54, y carga de demanda resultante.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-54, Tabla 220-54</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4319,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4771,6 +4771,48 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>N-010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cuadro de Cargas Jardin de Eventos CENTURA (Rev 5-feb-2026) -- validacion masiva de los 86 circuitos reales de los 8 tableros contra ElectroNOM, con foco en el interruptor de los 19 circuitos dedicados de motor (Art. 430-52).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cuadro de Cargas electricas Jardin de Eventos Centura, Rev 5-feb-2026. Se extrajeron y normalizaron los 86 circuitos reales de los 8 tableros (A, B, B(3F), B1(3F), C(3F), C1(3F), D(3F), TP) y se corrieron contra ElectroNOM. De esos, 19 son circuitos DEDICADOS de motor (manejadoras, condensadoras, aires acondicionados, boiler, extractores como circuito propio -- no cuenta un ventilador/extractor que aparece de paso dentro de un circuito general de iluminacion o contactos, eso NO es un circuito de motor por Art. 430).
+Se verifico el INTERRUPTOR de cada uno contra la Tabla 430-52 (fila general: motores monofasicos/polifasicos comunes), usando 250% de la corriente a plena carga (FLC) para interruptor de tiempo inverso -- los tableros del proyecto son Square D tipo QO, termomagneticos estandar, que caen en esa columna.
+4 circuitos EXCEDEN el maximo permitido por la tabla:
+  C.C. A, CT1 'Manejadora recamara principal' ... FLC 6.0 A x 250% = 15 A -&gt; instalado 20 A
+  C.C. A, CT5 'Manejadora recamara 2' .......... FLC 6.0 A x 250% = 15 A -&gt; instalado 20 A
+  C.C. A, CT17 'Manejadora recamara planta alta'  FLC 4.0 A x 250% = 10 A -&gt; redondea a 15 A -&gt; instalado 20 A
+  C.C. B1(3F), CT3 'Extractores baños hombres/mujeres' FLC 1.57 A x 250% = 3.9 A -&gt; redondea a 15 A -&gt; instalado 20 A
+Los otros 15 circuitos de motor (condensadoras, aires acondicionados de C, boiler, manejadoras de mayor corriente) SI cumplen: su 250%xFLC redondea de forma natural a 20 A o mas, coincidiendo con o superando el interruptor instalado.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Art. 430-52: el dispositivo de proteccion contra cortocircuito/falla a tierra del circuito derivado del motor NO DEBE EXCEDER el porcentaje de la Tabla 430-52 (redondeado al siguiente valor estandar si el calculo no cae en uno). Para interruptor de tiempo inverso (caso de este proyecto, tableros QO): 250% de FLC.
+En los 4 casos senalados, el patron es el mismo: son motores pequenos (FLC de 1.6 a 6 A) donde 250%xFLC da un maximo permitido de 15 A (el minimo escalon de la tabla de interruptores estandar), pero se instalo 20 A -- un escalon arriba del maximo que permite la norma. No es un caso de 'no corresponde a un tamano estandar' (15 A SI es un tamano estandar disponible), asi que la excepcion de 430-52(c)(1) para redondear hacia arriba no aplica aqui.
+Hipotesis mas probable (no confirmada, es interpretacion): para motores muy pequenos es practica comun de oficina usar el mismo criterio del circuito general (12 AWG / 20 A estandar) en vez de calcular el porcentaje exacto de la Tabla 430-52, similar al patron ya visto en N-002 (interruptor igualado a la ampacidad de tabla del conductor, no al calculo puntual de la norma).</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Los conductores de estos 4 circuitos SI estan bien (12 AWG soporta 20 A de sobra para motores de 1.6-7.5 A de FLC con el 125% de 430-22). El riesgo tecnico real es que el interruptor de 20 A puede no despejar una falla de cortocircuito tan rapido/selectivo como uno de 15 A calculado especificamente para ese motor pequeno -- un margen de proteccion mas amplio que el que permite la tabla, no una condicion insegura en si misma (a diferencia de N-005, donde la tierra estaba genuinamente subdimensionada). Es un hallazgo de apego estricto a la norma, no de seguridad inmediata.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ABIERTA (23-ago-2026), pendiente del criterio de Cesar -- mismo patron que N-002/N-006: decidir si mantener el criterio de oficina (12 AWG/20 A estandar para motores pequenos) o corregir a lo que calcula estrictamente la Tabla 430-52 (15 A) en los 4 circuitos senalados. No se modifico ningun documento del proyecto -- son entregables de Cesar.
+Metodologia y script quedan documentados en la memoria de la sesion (normalizar_centura.py + validar_motores.js); los archivos temporales no se conservan entre sesiones y hay que regenerarlos si se retoma este analisis.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -4344,6 +4344,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -4809,7 +4810,14 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>ABIERTA (23-ago-2026), pendiente del criterio de Cesar -- mismo patron que N-002/N-006: decidir si mantener el criterio de oficina (12 AWG/20 A estandar para motores pequenos) o corregir a lo que calcula estrictamente la Tabla 430-52 (15 A) en los 4 circuitos senalados. No se modifico ningun documento del proyecto -- son entregables de Cesar.
-Metodologia y script quedan documentados en la memoria de la sesion (normalizar_centura.py + validar_motores.js); los archivos temporales no se conservan entre sesiones y hay que regenerarlos si se retoma este analisis.</t>
+Metodologia y script quedan documentados en la memoria de la sesion (normalizar_centura.py + validar_motores.js); los archivos temporales no se conservan entre sesiones y hay que regenerarlos si se retoma este analisis.
+CERRADA (23-ago-2026). Decision de Cesar: seguir estrictamente lo que dice la NOM (Tabla 430-52), no el criterio de oficina.
+ACCION PENDIENTE EN EL PROYECTO (no realizada por esta herramienta -- son documentos de responsiva de Cesar): corregir el interruptor de los 4 circuitos senalados de 20 A a 15 A:
+  C.C. A, CT1  'Manejadora recamara principal'          -&gt; 15 A
+  C.C. A, CT5  'Manejadora recamara 2'                  -&gt; 15 A
+  C.C. A, CT17 'Manejadora recamara planta alta'         -&gt; 15 A
+  C.C. B1(3F), CT3 'Extractores banos hombres/mujeres'   -&gt; 15 A
+CRITERIO GENERAL QUE DEJA ESTA NOTA: para circuitos de motor, el interruptor se calcula con el porcentaje de la Tabla 430-52 segun el tipo de dispositivo (250% para interruptor de tiempo inverso en tableros termomagneticos estandar como los QO de este proyecto), NO con el criterio de oficina de usar 12 AWG/20 A por default. Motores pequenos (FLC bajo) son los que mas facilmente quedan sobredimensionados con ese habito, porque 20 A es el escalon minimo 'comodo' independientemente de que tan chico sea el motor.</t>
         </is>
       </c>
     </row>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2300,6 +2300,90 @@
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>220-55</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Factor de demanda de cocina en vivienda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Unidad de vivienda con estufa electrica, horno de pared, parrilla montada en el mueble de cocina u otro aparato de coccion de capacidad individual mayor a 1.75 kW.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aplicar el factor de demanda de la Tabla 220-55 segun la cantidad de aparatos. Metodo por defecto (Columna C, obligatorio salvo la Nota 3): demanda maxima en kW por cantidad de aparatos, valida hasta 12 kW por aparato. Alternativa permitida por la Nota 3 para aparatos de mas de 1.75 kW hasta 8.75 kW: sumar la potencia nominal de los aparatos y multiplicarla por el factor de la Columna A (menos de 3.5 kW) o B (3.5 a 8.75 kW) segun la cantidad -- suele dar una demanda menor. Estufas individuales de mas de 12 kW, o de distinta capacidad nominal por encima de 8.75 kW, requieren los ajustes de las Notas 1 y 2 (no implementados en ElectroNOM).</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Memoria con: cantidad de aparatos, potencia nominal por aparato, metodo aplicado (Columna C o Nota 3) y demanda resultante.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-55, Tabla 220-55</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>220-56</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Factor de demanda de cocina comercial</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Inmueble que NO es unidad de vivienda, con equipo de coccion, calentadores de agua de lavaplatos u otros equipos de cocina controlados por termostato o de uso intermitente (no aplica a calefaccion, ventilacion ni aire acondicionado).</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aplicar el factor de demanda de la Tabla 220-56 segun la cantidad de equipos (100% para 1-2, 90% para 3, 80% para 4, 70% para 5, 65% para 6 o mas). La carga de demanda resultante NUNCA debe ser menor que la suma de las cargas de los dos equipos de cocina mas grandes (piso normativo explicito del Art. 220-56).</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Memoria con: cantidad de equipos, VA instalados, factor de demanda aplicado, suma de las 2 cargas mas grandes y demanda resultante (indicando si se aplico el piso).</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NOM-001-SEDE-2018, Articulo 220-56, Tabla 220-56</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Borrador</t>
         </is>
@@ -3206,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3772,6 +3856,463 @@
         <is>
           <t>Carga minima por secadora: 5000 VA o la placa de datos, la que sea mayor (Art. 220-54).</t>
         </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tabla 220-55.- Factores de demanda para estufas electricas domesticas, hornos de pared y otros aparatos de coccion de mas de 1.75 kW (vivienda). Solo transcrito de 1 a 25 aparatos: filas 26 en adelante del documento fuente traen formulas en celdas combinadas cuyo alcance por fila es ambiguo, no se transcriben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Numero de aparatos</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Columna A % (&lt;3.5 kW)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Columna B % (3.5-8.75 kW)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Columna C - Demanda maxima kW (hasta 12 kW, todos los casos salvo Nota 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80</v>
+      </c>
+      <c r="C62" t="n">
+        <v>80</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="n">
+        <v>75</v>
+      </c>
+      <c r="C63" t="n">
+        <v>65</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="n">
+        <v>70</v>
+      </c>
+      <c r="C64" t="n">
+        <v>55</v>
+      </c>
+      <c r="D64" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="n">
+        <v>66</v>
+      </c>
+      <c r="C65" t="n">
+        <v>50</v>
+      </c>
+      <c r="D65" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>62</v>
+      </c>
+      <c r="C66" t="n">
+        <v>45</v>
+      </c>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="n">
+        <v>59</v>
+      </c>
+      <c r="C67" t="n">
+        <v>43</v>
+      </c>
+      <c r="D67" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56</v>
+      </c>
+      <c r="C68" t="n">
+        <v>40</v>
+      </c>
+      <c r="D68" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="n">
+        <v>53</v>
+      </c>
+      <c r="C69" t="n">
+        <v>36</v>
+      </c>
+      <c r="D69" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" t="n">
+        <v>51</v>
+      </c>
+      <c r="C70" t="n">
+        <v>35</v>
+      </c>
+      <c r="D70" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="n">
+        <v>49</v>
+      </c>
+      <c r="C71" t="n">
+        <v>34</v>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" t="n">
+        <v>47</v>
+      </c>
+      <c r="C72" t="n">
+        <v>32</v>
+      </c>
+      <c r="D72" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" t="n">
+        <v>45</v>
+      </c>
+      <c r="C73" t="n">
+        <v>32</v>
+      </c>
+      <c r="D73" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="n">
+        <v>43</v>
+      </c>
+      <c r="C74" t="n">
+        <v>32</v>
+      </c>
+      <c r="D74" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" t="n">
+        <v>41</v>
+      </c>
+      <c r="C75" t="n">
+        <v>32</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" t="n">
+        <v>40</v>
+      </c>
+      <c r="C76" t="n">
+        <v>32</v>
+      </c>
+      <c r="D76" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" t="n">
+        <v>39</v>
+      </c>
+      <c r="C77" t="n">
+        <v>28</v>
+      </c>
+      <c r="D77" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" t="n">
+        <v>38</v>
+      </c>
+      <c r="C78" t="n">
+        <v>28</v>
+      </c>
+      <c r="D78" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" t="n">
+        <v>37</v>
+      </c>
+      <c r="C79" t="n">
+        <v>28</v>
+      </c>
+      <c r="D79" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" t="n">
+        <v>36</v>
+      </c>
+      <c r="C80" t="n">
+        <v>28</v>
+      </c>
+      <c r="D80" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" t="n">
+        <v>35</v>
+      </c>
+      <c r="C81" t="n">
+        <v>28</v>
+      </c>
+      <c r="D81" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>21</v>
+      </c>
+      <c r="B82" t="n">
+        <v>34</v>
+      </c>
+      <c r="C82" t="n">
+        <v>26</v>
+      </c>
+      <c r="D82" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" t="n">
+        <v>33</v>
+      </c>
+      <c r="C83" t="n">
+        <v>26</v>
+      </c>
+      <c r="D83" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" t="n">
+        <v>32</v>
+      </c>
+      <c r="C84" t="n">
+        <v>26</v>
+      </c>
+      <c r="D84" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" t="n">
+        <v>31</v>
+      </c>
+      <c r="C85" t="n">
+        <v>26</v>
+      </c>
+      <c r="D85" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" t="n">
+        <v>30</v>
+      </c>
+      <c r="C86" t="n">
+        <v>26</v>
+      </c>
+      <c r="D86" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Nota 3: en vez de Columna C, para aparatos de mas de 1.75 kW hasta 8.75 kW se permite sumar la potencia nominal y multiplicarla por el factor de Columna A o B segun la cantidad de aparatos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tabla 220-56.- Factores de demanda para equipos de cocina en inmuebles que NO son vivienda (cocina comercial). La demanda nunca debe ser menor que la suma de las dos cargas de equipo mas grandes (Art. 220-56).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Numero de unidades de equipo</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Factor de demanda (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>6 y mas</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4344,7 +4885,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/reglas-normativas/reglas_normativas.xlsx
+++ b/reglas-normativas/reglas_normativas.xlsx
@@ -3858,7 +3858,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -4245,7 +4244,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -4860,7 +4858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5361,6 +5359,50 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cuadro de Cargas Jardin de Eventos CENTURA (Rev 5-feb-2026) -- verificacion de caida de tension de los 7 circuitos 3F que traen distancia individual declarada en el cuadro (alimentadores entre tableros y derivados de aire acondicionado), pendiente desde la re-validacion masiva del 23-ago-2026 (N-010).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Se identificaron 7 circuitos trifasicos con distancia propia en el cuadro de cargas Rev5: TP-&gt;Centro de carga B (10 m, cedula 3F-8), TP-&gt;Centro de carga C (45 m, 3F-4), TP-&gt;Centro de carga D (130 m, 3F-8), C.C.B-&gt;Centro de carga B1 (20 m, 3F-12), C.C.C-&gt;Centro de carga C1 (10 m, 3F-10), C.C.C-&gt;Aire acondicionado 1 salon (10 m, 3F-12), C.C.C-&gt;Aire acondicionado 2 salon (25 m, 3F-12). El calibre de fase de la cedula se verifico contra el 3% de caida de tension (calcularCaidaTension de motor.js) usando la V.A. total del circuito TAL COMO la declara el archivo, SIN reproducir la columna AMPS propia del archivo de CENTURA.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Metodologia (instruccion expresa de Cesar: 'el archivo de CENTURA puede tener errores, confirma los resultados en base al software' -- no replicar su columna AMPS, calcular desde cero con ElectroNOM):
+1) Se detecto que la columna AMPS del archivo de CENTURA NO es reproducible con la formula trifasica estandar I = VA/(raiz3 x V): el cociente V.A./AMPS da ~342.56 de forma constante en las 7 filas, que no corresponde a 220 V (da 381.05) ni a ninguna combinacion V x FP declarada en el archivo. No se investigo mas a fondo el origen de esa cifra porque no es relevante: la instruccion es no confiar en esa columna, sino recalcular.
+2) Corriente usada: I = V.A. / (raiz3 x 220), formula estandar trifasica, la MISMA que usa systemMeta() en motor.js (vDenom = raiz3 para sistemas trifasicos) para cualquier carga capturada en la Calculadora. FP = 0.9 (supuesto explicito, no declarado en el archivo fuente; coincide con el valor por defecto de la UI de ElectroNOM). Esta combinacion (VA completo sin factor de demanda, FP 0.9) es CONSERVADORA: da una corriente igual o mayor a la que resultaria aplicando cualquier factor de demanda, por lo que el %VD calculado es un techo, no un piso.
+3) Resultado (calcularCaidaTension, Tabla 9 PVC/cobre, raiz3, 220 V, FP 0.9):
+   TP-&gt;Centro de carga B  (8 AWG,  10 m, 25.72 A) .... 0.48% -- CUMPLE
+   TP-&gt;Centro de carga C  (4 AWG,  45 m, 65.71 A) .... 2.30% -- CUMPLE
+   TP-&gt;Centro de carga D  (8 AWG, 130 m, 12.18 A) .... 2.96% -- CUMPLE (margen estrecho, ver nota)
+   C.C.B-&gt;Centro de carga B1 (12 AWG, 20 m, 17.85 A) . 1.69% -- CUMPLE
+   C.C.C-&gt;Centro de carga C1 (10 AWG, 10 m, 26.35 A) . 0.74% -- CUMPLE
+   C.C.C-&gt;AA 1 salon principal (12 AWG, 10 m, 13.12 A) 0.62% -- CUMPLE
+   C.C.C-&gt;AA 2 salon principal (12 AWG, 25 m, 13.12 A) 1.55% -- CUMPLE
+4) NOTA SOBRE TP-&gt;Centro de carga D: este circuito YA fue validado con mucho mayor detalle en N-001 (corriente real 10.9 A, considerando factor de demanda de oficina 0.8), que cerro en 8 AWG = 2.65% de caida, confirmado ademas por la revision de febrero de forma independiente. El 2.96% de esta nota usa a proposito una corriente MAS ALTA (12.18 A, sin factor de demanda) como verificacion conservadora adicional: incluso en ese escenario mas exigente, el 8 AWG sigue cumpliendo, aunque con margen estrecho (se voltearia a NO CUMPLE con FP &gt;= ~0.92 en vez de 0.9). No se abre una nota nueva sobre este circuito: se confirma lo que N-001 ya cerro, con un margen de seguridad adicional documentado.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Los 7 circuitos cumplen el limite de 3% de caida de tension con el calibre de fase que trae la cedula de cableado del cuadro Rev5. No se encontro ningun calibre insuficiente por caida de tension en esta revision. Unico punto a vigilar: TP-&gt;Centro de carga D tiene el margen mas estrecho de los 7 (bajo el supuesto conservador de esta nota), consistente con ser tambien el circuito de mayor distancia (130 m).</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CERRADA (30-ago-2026). Cierra el pendiente dejado por la re-validacion masiva del 23-ago-2026 (N-010): 'verificar caida de tension en los circuitos 3F que si traen distancia por circuito, no solo en los alimentadores entre tableros'. Los 7 circuitos con distancia individual declarada en el cuadro Rev5 cumplen el 3% de la NOM con el calibre que ya traen. No se requiere ninguna correccion en los documentos del proyecto.
+CRITERIO GENERAL QUE DEJA ESTA NOTA: cuando un archivo de un tercero trae una columna de corriente ya calculada, no asumir que es correcta ni tratar de reproducir su formula -- recalcular la corriente desde la potencia (V.A.) declarada usando la formula estandar del propio motor.js, y usar el supuesto mas conservador razonable (aqui: VA completo sin demanda, FP 0.9) cuando falte un dato declarado explicitamente en el archivo fuente.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
